--- a/request_forms/022_identity_badge_request_form--request_forms.xlsx
+++ b/request_forms/022_identity_badge_request_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -945,8 +945,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -974,12 +974,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'accounting'}</t>
+          <t>accounting</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Accounting'}</t>
+          <t>Accounting</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'engineering'}</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Engineering'}</t>
+          <t>Engineering</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'day_shift'}</t>
+          <t>day_shift</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Day Shift'}</t>
+          <t>Day Shift</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'night_shift'}</t>
+          <t>night_shift</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Night Shift'}</t>
+          <t>Night Shift</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'rotating_shift'}</t>
+          <t>rotating_shift</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Rotating Shift'}</t>
+          <t>Rotating Shift</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'standard'}</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Standard'}</t>
+          <t>Standard</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'senior'}</t>
+          <t>senior</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Senior'}</t>
+          <t>Senior</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'approve'}</t>
+          <t>approve</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Approve'}</t>
+          <t>Approve</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'deny'}</t>
+          <t>deny</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Deny'}</t>
+          <t>Deny</t>
         </is>
       </c>
     </row>
